--- a/ig/main/ValueSet-JDV-J281-StatutsRessourcesMS.xlsx
+++ b/ig/main/ValueSet-JDV-J281-StatutsRessourcesMS.xlsx
@@ -147,7 +147,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R368-StatutRessource</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R368-StatutRessource/FHIR/TRE-R368-StatutRessource</t>
   </si>
 </sst>
 </file>
